--- a/docs/archive/results_20260806/depression_results_clean_detailed.xlsx
+++ b/docs/archive/results_20260806/depression_results_clean_detailed.xlsx
@@ -13,7 +13,8 @@
     <sheet name="EN vs Native MacroF1" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Merged vs Standalone MacroF1" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="DAIC Packed30 Family" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Provenance" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Gemma 4 DAIC" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Provenance" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5988,7 +5989,303 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I188"/>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Gemma 4 vs Qwen — DAIC official test (seed 1337, fold 0, strict teacher-forced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="110" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Gemma 4: google/gemma-4-12B-it revision 707f0a3b8a3c…, BF16 LoRA (288 decoder modules, rank 16/alpha 32), SDPA, gradient checkpointing, batch 1 x 32 accum x 4 GPUs. Campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae; source a6749b05 (clean main); PR #31; same manifest/split as the Qwen harmonized campaign (72e2dd204b91…/441333e0c888…). Evaluation: original_teacher_forced, harmonized_all_windows_full_coverage, subject mean-score, headline/binary_strict, INVALID counts as wrong (INVALID=0). Qwen column = canonical harmonized _r1 DAIC rows. One seed each — differences are observations, not variance estimates. All values recomputed locally from predictions_subject_level.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Modality</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Macro-F1</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Positive-F1</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Run / attempt / jobs</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Local evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.7631048387096775</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.6875000000000001</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.7872340425531915</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2; attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805; train 44518086 eval 44518087 (COMPLETED 0:0); selected epoch 3</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_text/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Qwen (harmonized _r1)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>harmonized_v1_…_daic_audio_text_r1 (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; retry registry retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/audio_text/daic/*/fold_0/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.7021276595744681</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only; attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2; train 44517565 eval 44517566 (COMPLETED 0:0); selected epoch n/a</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Qwen (harmonized _r1)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.5392</v>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>harmonized_v1_…_daic_audio_only_r1 (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; retry registry retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/audio_only/daic/*/fold_0/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.7552083333333333</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.7872340425531915</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only; attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3; train 44517484 eval 44517485 (COMPLETED 0:0); selected epoch 1</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Qwen (harmonized _r1)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.7353</v>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>harmonized_v1_…_daic_text_only_r1 (campaign harmonized_v1_prod_20260809T171705Z_d1e8130b; retry registry retry_r1_jobs.tsv)</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1/text_only/daic/*/fold_0/best_model/standalone_eval(_r1)/metrics_original_teacher_forced.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Positive-F1/accuracy/precision/recall are shown for Gemma only; the Qwen harmonized rows in the workbook carry macro-F1 (STANDALONE_QWEN) and the same binary-strict headline semantics (values: DAIC audio+text 0.7353, audio-only 0.5392, text-only 0.7353). audio_only Gemma predicted Non-depressed for all 47 subjects (degenerate but valid; run and evidence are sound). No winner is selected from test results.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14420,6 +14717,687 @@
         </is>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B189" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C189" s="15" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D189" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 macro-F1</t>
+        </is>
+      </c>
+      <c r="E189" s="16" t="n">
+        <v>0.7631048387096775</v>
+      </c>
+      <c r="F189" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G189" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H189" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_text/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I189" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON); Slurm COMPLETED 0:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B190" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C190" s="15" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D190" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 positive-F1</t>
+        </is>
+      </c>
+      <c r="E190" s="16" t="n">
+        <v>0.6875000000000001</v>
+      </c>
+      <c r="F190" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G190" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H190" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_text/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I190" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B191" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C191" s="15" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D191" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 accuracy</t>
+        </is>
+      </c>
+      <c r="E191" s="16" t="n">
+        <v>0.7872340425531915</v>
+      </c>
+      <c r="F191" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G191" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H191" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_text/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I191" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B192" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C192" s="15" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D192" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 confusion matrix</t>
+        </is>
+      </c>
+      <c r="E192" s="15" t="inlineStr">
+        <is>
+          <t>[[26, 7], [3, 11]]</t>
+        </is>
+      </c>
+      <c r="F192" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G192" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H192" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_text/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2/fold_0/best_model/standalone_eval/confusion_matrix.json</t>
+        </is>
+      </c>
+      <c r="I192" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B193" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C193" s="15" t="inlineStr">
+        <is>
+          <t>Audio + Text</t>
+        </is>
+      </c>
+      <c r="D193" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 invalid count</t>
+        </is>
+      </c>
+      <c r="E193" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G193" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H193" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_text/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json</t>
+        </is>
+      </c>
+      <c r="I193" s="17" t="inlineStr">
+        <is>
+          <t>invalid_subjects == 0 in metrics JSON and recomputation</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B194" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C194" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D194" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 macro-F1</t>
+        </is>
+      </c>
+      <c r="E194" s="16" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="F194" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G194" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H194" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I194" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON); Slurm COMPLETED 0:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B195" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C195" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D195" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 positive-F1</t>
+        </is>
+      </c>
+      <c r="E195" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G195" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H195" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I195" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B196" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C196" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D196" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 accuracy</t>
+        </is>
+      </c>
+      <c r="E196" s="16" t="n">
+        <v>0.7021276595744681</v>
+      </c>
+      <c r="F196" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G196" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H196" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I196" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B197" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C197" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D197" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 confusion matrix</t>
+        </is>
+      </c>
+      <c r="E197" s="15" t="inlineStr">
+        <is>
+          <t>[[33, 0], [14, 0]]</t>
+        </is>
+      </c>
+      <c r="F197" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G197" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H197" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/confusion_matrix.json</t>
+        </is>
+      </c>
+      <c r="I197" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B198" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C198" s="15" t="inlineStr">
+        <is>
+          <t>Audio only</t>
+        </is>
+      </c>
+      <c r="D198" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 invalid count</t>
+        </is>
+      </c>
+      <c r="E198" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G198" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H198" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/audio_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json</t>
+        </is>
+      </c>
+      <c r="I198" s="17" t="inlineStr">
+        <is>
+          <t>invalid_subjects == 0 in metrics JSON and recomputation</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B199" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C199" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D199" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 macro-F1</t>
+        </is>
+      </c>
+      <c r="E199" s="16" t="n">
+        <v>0.7552083333333333</v>
+      </c>
+      <c r="F199" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G199" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H199" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I199" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON); Slurm COMPLETED 0:0</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B200" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C200" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D200" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 positive-F1</t>
+        </is>
+      </c>
+      <c r="E200" s="16" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F200" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G200" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H200" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I200" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B201" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C201" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D201" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 accuracy</t>
+        </is>
+      </c>
+      <c r="E201" s="16" t="n">
+        <v>0.7872340425531915</v>
+      </c>
+      <c r="F201" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G201" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H201" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json + predictions_subject_level.csv</t>
+        </is>
+      </c>
+      <c r="I201" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B202" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C202" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D202" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 confusion matrix</t>
+        </is>
+      </c>
+      <c r="E202" s="15" t="inlineStr">
+        <is>
+          <t>[[27, 6], [4, 10]]</t>
+        </is>
+      </c>
+      <c r="F202" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G202" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H202" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/confusion_matrix.json</t>
+        </is>
+      </c>
+      <c r="I202" s="17" t="inlineStr">
+        <is>
+          <t>recomputed locally from predictions (matches metrics JSON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 DAIC</t>
+        </is>
+      </c>
+      <c r="B203" s="15" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="C203" s="15" t="inlineStr">
+        <is>
+          <t>Text only</t>
+        </is>
+      </c>
+      <c r="D203" s="15" t="inlineStr">
+        <is>
+          <t>Gemma 4 invalid count</t>
+        </is>
+      </c>
+      <c r="E203" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" s="17" t="inlineStr">
+        <is>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only, attempt 20260812T020449Z-gemma4_daic_text_only_seed1337-cca3f4ae-ed58a7a3, source a6749b05 (clean main), PR #31, jobs 44517484/44517485, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+        </is>
+      </c>
+      <c r="G203" s="17" t="inlineStr">
+        <is>
+          <t>official 47-subject test, subject mean-score, teacher-forced, binary-strict, harmonized_all_windows_full_coverage</t>
+        </is>
+      </c>
+      <c r="H203" s="17" t="inlineStr">
+        <is>
+          <t>output_model/harmonized_v1_gemma4/text_only/daic/gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_text_only/fold_0/best_model/standalone_eval/metrics_original_teacher_forced.json</t>
+        </is>
+      </c>
+      <c r="I203" s="17" t="inlineStr">
+        <is>
+          <t>invalid_subjects == 0 in metrics JSON and recomputation</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>

--- a/docs/archive/results_20260806/depression_results_clean_detailed.xlsx
+++ b/docs/archive/results_20260806/depression_results_clean_detailed.xlsx
@@ -6092,7 +6092,7 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2; attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805; train 44518086 eval 44518087 (COMPLETED 0:0); selected epoch 3</t>
+          <t>run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2; attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805; train 44518086 eval 44518087 (COMPLETED 0:0); selected epoch 3; first attempt 20260812T020449Z-gemma4_daic_audio_text_seed1337-cca3f4ae-5704f1f7 FAILED (train 44517567 CUDA OOM / eval 44517568 CANCELLED); superseded by this retry</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only; attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2; train 44517565 eval 44517566 (COMPLETED 0:0); selected epoch n/a</t>
+          <t>run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only; attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2; train 44517565 eval 44517566 (COMPLETED 0:0); selected epoch 1</t>
         </is>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -14743,7 +14743,7 @@
       </c>
       <c r="F189" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…; first attempt …-cca3f4ae-5704f1f7 FAILED (train 44517567, eval 44517568 CANCELLED), superseded by retry …-a6749b05-146c8805</t>
         </is>
       </c>
       <c r="G189" s="17" t="inlineStr">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="F190" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…; first attempt …-cca3f4ae-5704f1f7 FAILED (train 44517567, eval 44517568 CANCELLED), superseded by retry …-a6749b05-146c8805</t>
         </is>
       </c>
       <c r="G190" s="17" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="F191" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…; first attempt …-cca3f4ae-5704f1f7 FAILED (train 44517567, eval 44517568 CANCELLED), superseded by retry …-a6749b05-146c8805</t>
         </is>
       </c>
       <c r="G191" s="17" t="inlineStr">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="F192" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…; first attempt …-cca3f4ae-5704f1f7 FAILED (train 44517567, eval 44517568 CANCELLED), superseded by retry …-a6749b05-146c8805</t>
         </is>
       </c>
       <c r="G192" s="17" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="F193" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_text_r2, attempt 20260812T031624Z-gemma4_daic_audio_text_seed1337-a6749b05-146c8805, source a6749b05 (clean main), PR #31, jobs 44518086/44518087, selected epoch 3, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…; first attempt …-cca3f4ae-5704f1f7 FAILED (train 44517567, eval 44517568 CANCELLED), superseded by retry …-a6749b05-146c8805</t>
         </is>
       </c>
       <c r="G193" s="17" t="inlineStr">
@@ -14970,7 +14970,7 @@
       </c>
       <c r="F194" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
         </is>
       </c>
       <c r="G194" s="17" t="inlineStr">
@@ -15015,7 +15015,7 @@
       </c>
       <c r="F195" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
         </is>
       </c>
       <c r="G195" s="17" t="inlineStr">
@@ -15060,7 +15060,7 @@
       </c>
       <c r="F196" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
         </is>
       </c>
       <c r="G196" s="17" t="inlineStr">
@@ -15107,7 +15107,7 @@
       </c>
       <c r="F197" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
         </is>
       </c>
       <c r="G197" s="17" t="inlineStr">
@@ -15152,7 +15152,7 @@
       </c>
       <c r="F198" s="17" t="inlineStr">
         <is>
-          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch n/a, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
+          <t>campaign gemma4_v1_prod_20260812T020449Z_cca3f4ae, run gemma4_harmonized_v1_gemma4_v1_prod_20260812T020449Z_cca3f4ae_daic_audio_only, attempt 20260812T020449Z-gemma4_daic_audio_only_seed1337-cca3f4ae-8789edf2, source a6749b05 (clean main), PR #31, jobs 44517565/44517566, selected epoch 1, model google/gemma-4-12B-it rev 707f0a3b8a3c…, cfg/manifest/split 72e2dd204b91…/441333e0c888…</t>
         </is>
       </c>
       <c r="G198" s="17" t="inlineStr">
